--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="2775" windowWidth="15330" windowHeight="2655"/>
   </bookViews>
@@ -10,12 +15,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>有效状态</t>
   </si>
@@ -61,6 +65,10 @@
   </si>
   <si>
     <t>质押券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -139,7 +147,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -181,7 +189,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,7 +224,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -425,17 +433,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="10" width="15.625" customWidth="1"/>
-    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="2" customWidth="1"/>
-    <col min="13" max="14" width="15.625" customWidth="1"/>
-    <col min="15" max="19" width="9" customWidth="1"/>
+    <col min="1" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="15.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.625" style="2" customWidth="1"/>
+    <col min="14" max="15" width="15.625" customWidth="1"/>
+    <col min="16" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,31 +459,34 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>有效状态</t>
   </si>
@@ -65,10 +65,6 @@
   </si>
   <si>
     <t>质押券</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -433,17 +429,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="2" customWidth="1"/>
-    <col min="14" max="15" width="15.625" customWidth="1"/>
-    <col min="16" max="20" width="9" customWidth="1"/>
+    <col min="1" max="10" width="15.625" customWidth="1"/>
+    <col min="11" max="11" width="15.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="15.625" customWidth="1"/>
+    <col min="15" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,34 +455,31 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
       <c r="I1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
       <c r="N1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="15330" windowHeight="2655"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="15330" windowHeight="2660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>有效状态</t>
   </si>
@@ -69,6 +69,10 @@
   </si>
   <si>
     <t>合作资产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成交编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -433,17 +437,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="2" customWidth="1"/>
-    <col min="14" max="15" width="15.625" customWidth="1"/>
-    <col min="16" max="20" width="9" customWidth="1"/>
+    <col min="1" max="12" width="15.6328125" customWidth="1"/>
+    <col min="13" max="13" width="15.6328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6328125" style="2" customWidth="1"/>
+    <col min="15" max="16" width="15.6328125" customWidth="1"/>
+    <col min="17" max="21" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,39 +458,42 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20377"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BS\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965DBC27-A224-4945-B776-B4919A47EC53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="15330" windowHeight="2655"/>
+    <workbookView xWindow="0" yWindow="3135" windowWidth="15330" windowHeight="2655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,14 +65,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>质押券</t>
+    <t>债券名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
@@ -143,7 +144,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -218,6 +219,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -253,6 +271,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -428,7 +463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2780" windowWidth="15330" windowHeight="2660"/>
+    <workbookView xWindow="0" yWindow="2784" windowWidth="15336" windowHeight="2664"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,15 +59,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>质押券</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>成交编号</t>
+    <t>银行间成交编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>债券名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -139,6 +134,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -151,14 +214,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCEDC7"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -193,7 +256,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -228,7 +291,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -438,12 +501,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="15.6328125" customWidth="1"/>
-    <col min="13" max="13" width="15.6328125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.6328125" style="2" customWidth="1"/>
-    <col min="15" max="16" width="15.6328125" customWidth="1"/>
+    <col min="1" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="12" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15" max="16" width="15.6640625" customWidth="1"/>
     <col min="17" max="21" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -458,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -467,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdRepoTrade001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZNEW\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2784" windowWidth="15336" windowHeight="2664"/>
+    <workbookView xWindow="0" yWindow="2780" windowWidth="15340" windowHeight="2660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>有效状态</t>
   </si>
@@ -56,10 +61,6 @@
   </si>
   <si>
     <t>交易场所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -134,74 +135,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -214,14 +147,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCEDC7"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -256,7 +189,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -291,7 +224,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -500,19 +433,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
-    <col min="5" max="12" width="15.6640625" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" style="2" customWidth="1"/>
-    <col min="15" max="16" width="15.6640625" customWidth="1"/>
-    <col min="17" max="21" width="9" customWidth="1"/>
+    <col min="1" max="3" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="11" width="15.6328125" customWidth="1"/>
+    <col min="12" max="12" width="15.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6328125" style="2" customWidth="1"/>
+    <col min="14" max="15" width="15.6328125" customWidth="1"/>
+    <col min="16" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -531,34 +464,31 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>15</v>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="N1" t="s">
+        <v>6</v>
+      </c>
       <c r="O1" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" t="s">
         <v>8</v>
       </c>
     </row>
